--- a/downloads/loesungen/04_Schule_2NF_Loesung.xlsx
+++ b/downloads/loesungen/04_Schule_2NF_Loesung.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER" sheetId="1" r:id="R49e98324aef34f10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNTERRICHT" sheetId="2" r:id="R3a65648e2dbb4097"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER_UNTERRICHT" sheetId="3" r:id="Rb19bde642f42402a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER" sheetId="1" r:id="Re3ad76d296c04bd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNTERRICHT" sheetId="2" r:id="R1825d6a1c2a548d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER_UNTERRICHT" sheetId="3" r:id="R1b5dfb39be544528"/>
   </x:sheets>
 </x:workbook>
 </file>
